--- a/stories/arbres/TREE-SEC-015.xlsx
+++ b/stories/arbres/TREE-SEC-015.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lina est au bord de la mer. Maman est là. Ils sont sur le balcon. Les pieds restent au sol. On reste derrière la protection. Maman est l'adulte. Les mains tiennent le doudou. Papa apporte l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit le chat, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1869,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -2009,6 +2046,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2195,6 +2237,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2361,6 +2408,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. On entend la mer. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2549,6 +2601,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2717,6 +2774,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un oiseau chante. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2879,6 +2941,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,6 +3112,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Le bois du balcon est chaud. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3207,6 +3279,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3373,6 +3450,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. L'eau chuchote. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3535,6 +3617,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3701,6 +3788,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Le vent est doux. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3889,6 +3981,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -4057,6 +4154,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le bois du balcon est chaud. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4219,6 +4321,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4385,6 +4492,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. L'eau chuchote. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4547,6 +4659,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4713,6 +4830,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un bateau souffle loin. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4875,6 +4997,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5041,6 +5168,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Un oiseau chante. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5229,6 +5361,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5397,6 +5534,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5559,6 +5701,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5725,6 +5872,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5887,6 +6039,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6053,6 +6210,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6215,6 +6377,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6381,6 +6548,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit le chien, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6565,6 +6737,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -6737,6 +6914,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6923,6 +7105,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7089,6 +7276,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. Le bois du balcon est chaud. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7277,6 +7469,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -7445,6 +7642,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Le bois du balcon est chaud. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7607,6 +7809,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7773,6 +7980,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. L'eau chuchote. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7935,6 +8147,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8101,6 +8318,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un bateau souffle loin. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8263,6 +8485,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8429,6 +8656,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. L'eau chuchote. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8617,6 +8849,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8785,6 +9022,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8947,6 +9189,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9113,6 +9360,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9275,6 +9527,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9441,6 +9698,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9603,6 +9865,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9769,6 +10036,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Un bateau souffle loin. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9957,6 +10229,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -10125,6 +10402,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un bateau souffle loin. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10287,6 +10569,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10453,6 +10740,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. On entend la mer. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10615,6 +10907,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10781,6 +11078,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le vent est doux. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10943,6 +11245,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11109,6 +11416,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina voit la poule, dans un jardin. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11293,6 +11605,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
     </row>
@@ -11465,6 +11782,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11651,6 +11973,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11817,6 +12144,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le bac à sable. On entend la mer. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12005,6 +12337,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12173,6 +12510,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12335,6 +12677,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12501,6 +12848,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12663,6 +13015,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12829,6 +13186,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12991,6 +13353,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13157,6 +13524,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le toboggan. Le vent est doux. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13345,6 +13717,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -13513,6 +13890,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. Un bateau souffle loin. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13675,6 +14057,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13841,6 +14228,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. On entend la mer. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14003,6 +14395,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14169,6 +14566,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Le vent est doux. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14331,6 +14733,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14497,6 +14904,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi les balançoires. Un oiseau chante. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14685,6 +15097,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14853,6 +15270,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit rouge. On entend la mer. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15015,6 +15437,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15181,6 +15608,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit bleu. Le vent est doux. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15343,6 +15775,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15509,6 +15946,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina choisit vert. Un oiseau chante. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15671,6 +16113,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15689,7 +16136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15762,6 +16209,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SEC-015.xlsx
+++ b/stories/arbres/TREE-SEC-015.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lina est au bord de la mer. Maman est là. Ils sont sur le balcon. Les pieds restent au sol. On reste derrière la protection. Maman est l'adulte. Les mains tiennent le doudou. Papa apporte l'eau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1512,6 +1518,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1685,6 +1696,7 @@
           <t>narrateur|Lina voit le chat, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1876,6 +1888,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2051,6 +2064,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2242,6 +2256,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2413,6 +2428,7 @@
           <t>narrateur|Lina a choisi le bac à sable. On entend la mer. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2608,6 +2624,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2779,6 +2796,7 @@
           <t>narrateur|Lina choisit rouge. Un oiseau chante. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2946,6 +2964,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3117,6 +3136,7 @@
           <t>narrateur|Lina choisit bleu. Le bois du balcon est chaud. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3284,6 +3304,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3455,6 +3476,7 @@
           <t>narrateur|Lina choisit vert. L'eau chuchote. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3622,6 +3644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3793,6 +3816,7 @@
           <t>narrateur|Lina a choisi le toboggan. Le vent est doux. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3988,6 +4012,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4159,6 +4184,7 @@
           <t>narrateur|Lina choisit rouge. Le bois du balcon est chaud. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4326,6 +4352,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4497,6 +4524,7 @@
           <t>narrateur|Lina choisit bleu. L'eau chuchote. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4664,6 +4692,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4835,6 +4864,7 @@
           <t>narrateur|Lina choisit vert. Un bateau souffle loin. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5002,6 +5032,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5173,6 +5204,7 @@
           <t>narrateur|Lina a choisi les balançoires. Un oiseau chante. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5368,6 +5400,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5539,6 +5572,7 @@
           <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5706,6 +5740,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5877,6 +5912,7 @@
           <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6044,6 +6080,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6215,6 +6252,7 @@
           <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6382,6 +6420,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6553,6 +6592,11 @@
           <t>narrateur|Lina voit le chien, depuis le balcon. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6744,6 +6788,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6919,6 +6964,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7110,6 +7156,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7281,6 +7328,7 @@
           <t>narrateur|Lina a choisi le bac à sable. Le bois du balcon est chaud. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7476,6 +7524,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7647,6 +7696,7 @@
           <t>narrateur|Lina choisit rouge. Le bois du balcon est chaud. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7814,6 +7864,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7985,6 +8036,7 @@
           <t>narrateur|Lina choisit bleu. L'eau chuchote. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8152,6 +8204,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8323,6 +8376,7 @@
           <t>narrateur|Lina choisit vert. Un bateau souffle loin. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8490,6 +8544,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8661,6 +8716,7 @@
           <t>narrateur|Lina a choisi le toboggan. L'eau chuchote. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8856,6 +8912,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9027,6 +9084,7 @@
           <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9194,6 +9252,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9365,6 +9424,7 @@
           <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9532,6 +9592,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9703,6 +9764,7 @@
           <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9870,6 +9932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -10041,6 +10104,7 @@
           <t>narrateur|Lina a choisi les balançoires. Un bateau souffle loin. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10236,6 +10300,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10407,6 +10472,7 @@
           <t>narrateur|Lina choisit rouge. Un bateau souffle loin. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10574,6 +10640,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10745,6 +10812,7 @@
           <t>narrateur|Lina choisit bleu. On entend la mer. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10912,6 +10980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11083,6 +11152,7 @@
           <t>narrateur|Lina choisit vert. Le vent est doux. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11250,6 +11320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11421,6 +11492,7 @@
           <t>narrateur|Lina voit la poule, dans un jardin. Pieds au sol. Derrière la protection. Avec Maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11612,6 +11684,7 @@
           <t>narrateur|Les pieds sont où ? Au sol.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11787,6 +11860,7 @@
           <t>narrateur|Oui. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina retient : pieds au sol, protection, adulte. Les mains tiennent un jouet, près de Maman. On continue, avec Maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11978,6 +12052,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12149,6 +12224,7 @@
           <t>narrateur|Lina a choisi le bac à sable. On entend la mer. Lina a un petit bac à sable sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12344,6 +12420,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12515,6 +12592,7 @@
           <t>narrateur|Lina choisit rouge. L'eau chuchote. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12682,6 +12760,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12853,6 +12932,7 @@
           <t>narrateur|Lina choisit bleu. Un bateau souffle loin. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -13020,6 +13100,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13191,6 +13272,7 @@
           <t>narrateur|Lina choisit vert. On entend la mer. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13358,6 +13440,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13529,6 +13612,7 @@
           <t>narrateur|Lina a choisi le toboggan. Le vent est doux. Lina a un petit toboggan jouet sur le sol. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13724,6 +13808,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13895,6 +13980,7 @@
           <t>narrateur|Lina choisit rouge. Un bateau souffle loin. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -14062,6 +14148,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14233,6 +14320,7 @@
           <t>narrateur|Lina choisit bleu. On entend la mer. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14400,6 +14488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14571,6 +14660,7 @@
           <t>narrateur|Lina choisit vert. Le vent est doux. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14738,6 +14828,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14909,6 +15000,7 @@
           <t>narrateur|Lina a choisi les balançoires. Un oiseau chante. Lina a de petites balançoires jouet. Pieds au sol. Derrière la protection. Avec l'adulte. Les mains tiennent un jouet, près de Maman. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -15104,6 +15196,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15275,6 +15368,7 @@
           <t>narrateur|Lina choisit rouge. On entend la mer. Lina tient le seau rouge. Pieds au sol. Derrière la protection. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15442,6 +15536,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15613,6 +15708,7 @@
           <t>narrateur|Lina choisit bleu. Le vent est doux. Lina tient le seau bleu. Pieds au sol. Avec l'adulte. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15780,6 +15876,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15951,6 +16048,7 @@
           <t>narrateur|Lina choisit vert. Un oiseau chante. Lina tient le seau vert. Pieds au sol. Derrière la protection, avec Maman. Les pieds restent au sol. On reste derrière la protection. On est avec l'adulte. Lina dit merci à Maman. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16118,6 +16216,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16136,7 +16235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16216,6 +16315,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16230,7 +16343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16417,6 +16530,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
